--- a/docs/sdk-test-report.xlsx
+++ b/docs/sdk-test-report.xlsx
@@ -11587,7 +11587,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>FAILED - 4 of 5 steps. Run 2026-09-24 07:20 (UTC+8). 26.43s. billable - launched a real sandbox. Failure: AssertionError: one logical launch produced more than one sandbox: {'resent': 2, 'three at once': 3, 'abandoned, then retried': 2} (expected 1 each). launch() takes no idempotency key, request id or client token, and display_name does not deduplicate, so a CI job that retries after a dropped connection pays for both — and the abandoned one is not discoverable from anything the caller kept
+          <t>FAILED - 4 of 5 steps. Run 2026-09-24 07:43 (UTC+8). 26.92s. billable - launched a real sandbox. Failure: AssertionError: one logical launch produced more than one sandbox: {'resent': 2, 'three at once': 3, 'abandoned, then retried': 2} (expected 1 each). launch() takes no idempotency key, request id or client token, and display_name does not deduplicate, so a CI job that retries after a dropped connection pays for both — and the abandoned one is not discoverable from anything the caller kept
 assert not {'resent': 2, 'three at once': 3, 'abandoned, then retried': 2}</t>
         </is>
       </c>
@@ -11662,21 +11662,21 @@
 {
   "count": 2,
   "first": {
-    "elapsed_s": 2.02,
-    "id": "f4a16f94-7d97-4a74-b953-5fd2c8570c51",
+    "elapsed_s": 2.81,
+    "id": "0324c77f-13fc-4661-bc6c-bc64ffe6a85f",
     "ok": true
   },
   "sandboxes created": {
     "another agent, i.e. a concurrent run": [],
     "no agent at all": [],
     "this agent": [
-      "2d7fb06a-6a7f-4075-9c43-c515ff185270",
-      "f4a16f94-7d97-4a74-b953-5fd2c8570c51"
+      "0324c77f-13fc-4661-bc6c-bc64ffe6a85f",
+      "93b8561b-7989-4a7a-a1d1-fc4842b3c66d"
     ]
   },
   "second": {
     "elapsed_s": 1.74,
-    "id": "2d7fb06a-6a7f-4075-9c43-c515ff185270",
+    "id": "93b8561b-7989-4a7a-a1d1-fc4842b3c66d",
     "ok": true
   },
   "sent": 2
@@ -11706,18 +11706,18 @@
   "count": 3,
   "outcomes": [
     {
-      "elapsed_s": 2.22,
-      "id": "d2858441-f735-44db-b922-c752ec8be441",
+      "elapsed_s": 1.51,
+      "id": "d83290ee-f9fb-4fe7-bb07-5927aa086c59",
       "ok": true
     },
     {
-      "elapsed_s": 2.22,
-      "id": "b765b651-040e-4d97-8b60-994d3f8dedca",
+      "elapsed_s": 2.0,
+      "id": "c8a47b51-019d-4645-81c1-7ea4dab39d60",
       "ok": true
     },
     {
-      "elapsed_s": 1.44,
-      "id": "76c9e03a-2428-478c-89cd-b7c3e914dda5",
+      "elapsed_s": 2.1,
+      "id": "d752a188-ffef-4ce9-88a7-31ec0130c23d",
       "ok": true
     }
   ],
@@ -11725,9 +11725,9 @@
     "another agent, i.e. a concurrent run": [],
     "no agent at all": [],
     "this agent": [
-      "76c9e03a-2428-478c-89cd-b7c3e914dda5",
-      "b765b651-040e-4d97-8b60-994d3f8dedca",
-      "d2858441-f735-44db-b922-c752ec8be441"
+      "c8a47b51-019d-4645-81c1-7ea4dab39d60",
+      "d752a188-ffef-4ce9-88a7-31ec0130c23d",
+      "d83290ee-f9fb-4fe7-bb07-5927aa086c59"
     ]
   },
   "sent": 3
@@ -11754,26 +11754,26 @@
         <is>
           <t>PASSED
 {
-  "a healthy launch took_s": 2.02,
+  "a healthy launch took_s": 2.81,
   "count": 2,
   "created by the abandoned call": {
     "another agent, i.e. a concurrent run": [],
     "no agent at all": [],
     "this agent": [
-      "a0cb2a89-c7c9-49be-bdb2-c55ecb88bf45"
+      "7fd43f45-1202-462c-ad01-f15146b7afcb"
     ]
   },
   "sandboxes created in total": {
     "another agent, i.e. a concurrent run": [],
     "no agent at all": [],
     "this agent": [
-      "74088162-0723-48e5-9446-77d12642e315",
-      "a0cb2a89-c7c9-49be-bdb2-c55ecb88bf45"
+      "7fd43f45-1202-462c-ad01-f15146b7afcb",
+      "e2af2f57-dcfe-41c1-9471-28e0db0d8feb"
     ]
   },
   "scenario reproduced": true,
   "the abandoned call": {
-    "elapsed_s": 2.0,
+    "elapsed_s": 1.98,
     "message": "the request was sent in full and the connection was closed 1.5s later without reading the answer",
     "ok": false,
     "raised": "TransportError",
@@ -11781,8 +11781,8 @@
   },
   "the connection was closed after_s": 1.5,
   "the retry": {
-    "elapsed_s": 1.56,
-    "id": "74088162-0723-48e5-9446-77d12642e315",
+    "elapsed_s": 2.0,
+    "id": "e2af2f57-dcfe-41c1-9471-28e0db0d8feb",
     "ok": true
   }
 }</t>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>PASSED - 3 of 3 steps. Run 2026-09-24 07:20 (UTC+8). 76.80s. billable - launched a real sandbox</t>
+          <t>PASSED - 3 of 3 steps. Run 2026-09-24 07:43 (UTC+8). 66.75s. billable - launched a real sandbox</t>
         </is>
       </c>
     </row>
@@ -11890,33 +11890,25 @@
       "reached running": 7,
       "refused on the call": [
         {
-          "elapsed_s": 0.9,
+          "elapsed_s": 0.95,
           "index": 1,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-8b32552a-61f6-47c0-bc9e-060d1d3ec5bc\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-db0e0294-47bf-4127-8eb5-4f28d088c1a1\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
-          "elapsed_s": 0.89,
-          "index": 2,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-206d3f56-7600-497f-bff2-42f5234dbd9c\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "elapsed_s": 0.95,
+          "index": 3,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-eb596eb5-45e4-405d-b156-8d979755973c\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
-          "elapsed_s": 0.88,
-          "index": 4,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-288eed75-1d57-4afb-bd44-3fdf3dfb9c95\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.87,
+          "elapsed_s": 0.94,
           "index": 6,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-d39cbf11-b1e6-4e0c-b9ae-6a13216ad34d\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (6/5, reque",
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-bca59138-fba8-4006-a93e-4d305b0f3644\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
@@ -11924,31 +11916,39 @@
         {
           "elapsed_s": 0.91,
           "index": 7,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-c11d2507-b4e3-4ab1-8014-3430226ed9a5\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-521c100d-9942-49bc-a506-ebbafdd5a589\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
-          "elapsed_s": 0.87,
+          "elapsed_s": 0.96,
+          "index": 8,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-84d01bb8-253e-41d8-8d60-c744f0853838\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "ok": false,
+          "raised": "UnprocessableError",
+          "status_code": 422
+        },
+        {
+          "elapsed_s": 0.98,
           "index": 10,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-c01d8696-edab-4444-9f4c-8bc1725c9fa9\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-3d7a28dd-9655-49de-978b-81ba944fbe80\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
           "elapsed_s": 0.86,
-          "index": 12,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-b1d7fcff-205d-4501-b378-14e4d76a902f\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "index": 11,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-22bafcfe-beb0-4183-ad9d-9cf1aac23168\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
-          "elapsed_s": 0.92,
-          "index": 13,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-b6ad38c7-0b85-4eeb-9cdf-f42c445c18dc\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "elapsed_s": 0.91,
+          "index": 12,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-275b1bda-2050-4ca8-aef7-32cd24049524\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
@@ -11956,39 +11956,39 @@
         {
           "elapsed_s": 0.91,
           "index": 14,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-8e0b0d83-59c0-4de8-90fd-abaee8d867ea\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-e15f8e12-ab06-4636-8f7f-249241e0051d\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "ok": false,
+          "raised": "UnprocessableError",
+          "status_code": 422
+        },
+        {
+          "elapsed_s": 0.91,
+          "index": 16,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-571e0145-6146-4de6-89bf-30d8f6040194\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "ok": false,
+          "raised": "UnprocessableError",
+          "status_code": 422
+        },
+        {
+          "elapsed_s": 0.88,
+          "index": 17,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-f444a49f-ad3f-4725-812e-2f3ed6b9e556\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "ok": false,
+          "raised": "UnprocessableError",
+          "status_code": 422
+        },
+        {
+          "elapsed_s": 0.89,
+          "index": 19,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-1488acb0-aaf1-47a4-93dd-b08c020d55d3\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
           "elapsed_s": 0.9,
-          "index": 15,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-cd10065f-f1c4-48d9-bce4-11467b7b8e37\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.88,
-          "index": 16,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-883568d0-0883-49c1-a51e-34401a18d9c8\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.9,
-          "index": 18,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-95cdfdb5-1226-462f-870e-a2b570a3afc8\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.86,
-          "index": 19,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-173d6f15-9d23-4b13-872d-2ee00f2c7c07\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
+          "index": 20,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-1bf58075-17fd-41c6-9703-68f0a4b2e2f3\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (7/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
@@ -11996,21 +11996,23 @@
       ],
       "round": 1,
       "task records left by the refused launches": {
-        "belonging to another run, left alone": [],
+        "belonging to another run, left alone": [
+          "cad9fa0b-0723-4641-a91b-215c171ddbdf"
+        ],
         "ids": [
-          "02a729bb-ee31-47e9-821a-e99664bf78fb",
-          "39614c22-da7f-4366-a800-c0ef350566d2",
-          "4341d233-6bab-4b83-a0a7-b7a1ab3ed8b0",
-          "6c02da9e-129b-4a07-b680-c4344c972b49",
-          "7477e300-06f0-4394-b0fa-239a1dfbbeeb",
-          "84c9211b-8bdc-4c6c-b468-37212bff097c",
-          "885e6133-e4bd-4eb9-bc52-e6078a7bf9f8",
-          "bbd8350a-1280-4a16-9e40-9b87c027a93e",
-          "c3d93db8-c0a2-4e12-8b23-d2c4ce2570c1",
-          "c4b7e524-3465-4157-89c8-9f1714562bb8",
-          "c81c809c-d3a1-4a9f-9729-f25d293d1802",
-          "d2545b4c-7704-4e6d-8f1e-2ce9555a7139",
-          "e4d10407-721e-4240-a5e5-f8a676c6a982"
+          "00728329-4f47-4778-9a51-ee68825c37d3",
+          "2b307b72-15e5-4c7e-8b82-eb34106bdad2",
+          "3024db94-6948-4317-9ff6-6ebdd6b3b21c",
+          "317add30-f1ce-4996-b901-9e42c8db3fec",
+          "4494a8d1-5c53-42f6-ab5d-d76f71c70c61",
+          "4eb12a6a-d45d-4f09-bf95-a8ea3a800dd9",
+          "6583e9ec-7d1d-4aa0-83f2-6d7360fca798",
+          "67d2f688-e57d-4169-9eac-4518bbaaa7a9",
+          "6916b8e7-e7d3-43e5-9a55-0e3be6e4cd15",
+          "856e2c24-b9ad-41aa-a258-184d80124dc1",
+          "98c365e9-51d0-4621-a38d-3532dfa428dc",
+          "a8332728-a407-4680-8585-36134344bd02",
+          "ea3aaa57-a9c3-45b8-9013-e828643a7af5"
         ],
         "left behind": 13,
         "removed": {
@@ -12019,105 +12021,73 @@
         }
       },
       "what the accepted ones settled to": {
-        "0e7f4e95-39da-49b1-a725-42773f89b7cd": {
-          "reached": "running",
-          "seconds": 0.77
-        },
-        "9433703f-f17b-4ce4-8a3a-c67d607aec20": {
-          "reached": "running",
-          "seconds": 0.75
-        },
-        "98c28134-a6dd-4d74-9bfb-582e3f7ea582": {
-          "reached": "running",
-          "seconds": 0.82
-        },
-        "99d3e95f-7dce-4b8e-bfcb-64991dee4229": {
+        "2d1b958e-9924-4afe-ba57-d088002353b2": {
           "reached": "running",
           "seconds": 0.72
         },
-        "a8d041a7-459e-41c0-b6ad-e933e6f400d2": {
+        "59f7e41f-1e02-423a-9594-942bb0c00e12": {
           "reached": "running",
           "seconds": 0.72
         },
-        "e34d7014-3a3f-4d29-9c20-c6abfbffad1a": {
+        "8fe9a80f-d6e4-422b-b100-fb19bb37f710": {
           "reached": "running",
-          "seconds": 0.82
+          "seconds": 0.73
         },
-        "fdcbc7fc-77a6-4cdf-9f1f-d7f547dd7522": {
+        "903c5bae-5c9c-473a-957d-7b9c04bb85c9": {
           "reached": "running",
           "seconds": 0.79
+        },
+        "a8f0e05d-a18c-4df1-ba77-7951653abfd0": {
+          "reached": "running",
+          "seconds": 0.81
+        },
+        "cabaebe7-8196-4581-9165-b29a38cb1f1e": {
+          "reached": "running",
+          "seconds": 0.83
+        },
+        "d93869b5-73a6-4620-b726-b7f0a57c7580": {
+          "reached": "running",
+          "seconds": 0.72
         }
       }
     },
     {
-      "accepted": 5,
+      "accepted": 9,
       "cleanup": {
-        "deleted": 5,
+        "deleted": 9,
         "failed": []
       },
       "fired at once": 13,
-      "reached running": 5,
+      "reached running": 9,
       "refused on the call": [
         {
           "elapsed_s": 0.95,
           "index": 1,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-12cc5d9d-6049-425f-a14b-6a30368b4d4b\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-c2386d1f-6840-4207-88aa-d9dd6e0d324f\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (9/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
-          "elapsed_s": 0.97,
-          "index": 4,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-fd6fea8f-6d09-44ec-9c13-df575334d2dd\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.93,
-          "index": 5,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-ea0205e2-dcd8-4d1c-8f3c-dabc6b041537\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.9,
-          "index": 7,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-ec49d08e-2b4f-4076-b118-a257218ae9b4\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.89,
-          "index": 10,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-a599102d-905a-45eb-8e21-5eee90a2fd63\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
+          "elapsed_s": 0.96,
+          "index": 2,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-b21c140c-7c98-4f6d-b19d-ede05aa2e05a\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (9/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
           "elapsed_s": 0.91,
-          "index": 11,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-34e98f66-1345-43bc-9b15-5d39d5f46616\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
+          "index": 12,
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-0ad896bc-6f67-4c34-8811-951a639f3f06\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (9/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
         },
         {
-          "elapsed_s": 0.92,
-          "index": 12,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-641eaa21-c1c2-49ca-9dd0-1bdfdc209217\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.91,
+          "elapsed_s": 0.88,
           "index": 13,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-43a3a6e0-fc1f-44d5-b784-f5b33871f1b0\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
+          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-5191744b-f2a3-4c93-ae8e-efd69cbba5d5\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (6/5, reque",
           "ok": false,
           "raised": "UnprocessableError",
           "status_code": 422
@@ -12127,125 +12097,66 @@
       "task records left by the refused launches": {
         "belonging to another run, left alone": [],
         "ids": [
-          "23892a35-7800-4973-a622-39c9d0f6c451",
-          "41ddabe8-390b-4a5d-973a-d168bde10b6b",
-          "53f045f7-f53c-46a5-a020-37d7587dc2c7",
-          "6af4f23c-bacc-4adc-9ee4-87cc294588b6",
-          "76f905fe-7ffd-4d40-8453-fce3f61fb1ba",
-          "b9cc6dfc-291b-4cbe-b7c9-b428c883951c",
-          "d79b876e-bf01-4360-9ab1-7aedb6380f37",
-          "dad2fb71-aece-4d21-9018-2749ca1b7df6"
+          "0a48f4c9-70de-4581-a844-e2c8e4c451d5",
+          "2245701c-3a74-4fa0-9dd9-26906a81de52",
+          "4cbfcbe6-6748-4bed-8aaa-d32f94473387",
+          "9686587e-7570-4156-b184-c1c0c069aa5e"
         ],
-        "left behind": 8,
+        "left behind": 4,
         "removed": {
-          "deleted": 8,
+          "deleted": 4,
           "failed": []
         }
       },
       "what the accepted ones settled to": {
-        "39b3b997-76d1-4587-8808-aa56b2fc332a": {
+        "39f34309-4792-42be-845d-2fc13e4bed6e": {
           "reached": "running",
-          "seconds": 0.75
+          "seconds": 0.82
         },
-        "50595736-0f2a-4b57-8c21-e92fc1518644": {
+        "4bff9969-0d6d-4c5f-9d64-764ba998b414": {
           "reached": "running",
-          "seconds": 0.71
+          "seconds": 0.82
         },
-        "c6bea9ee-65c1-406c-beb6-f2f3145b6fc7": {
+        "788a27c2-411b-4af3-b435-e7a1c298fd7a": {
+          "reached": "running",
+          "seconds": 0.83
+        },
+        "810cda4a-a33c-41b3-ace5-85eb8bacbc63": {
           "reached": "running",
           "seconds": 0.72
         },
-        "e536208f-3cb9-4bc5-ae7c-277743596648": {
+        "93a137d9-af1d-422e-85de-7bd894110911": {
           "reached": "running",
-          "seconds": 0.73
+          "seconds": 0.82
         },
-        "f8e9d7c7-3531-402a-9484-4911906cdc5f": {
+        "96d26e2b-35d9-4796-bbe9-dbe5b8df54df": {
           "reached": "running",
-          "seconds": 0.84
+          "seconds": 0.78
+        },
+        "a59441b6-a4bc-4a1b-94a7-49f92fbbf458": {
+          "reached": "running",
+          "seconds": 0.72
+        },
+        "d15a7136-7d08-44ac-94d4-32cd2ea8facd": {
+          "reached": "running",
+          "seconds": 0.8
+        },
+        "dac186d5-0952-44f8-95df-b7e2f87f01d0": {
+          "reached": "running",
+          "seconds": 0.72
         }
       }
     },
     {
-      "accepted": 5,
+      "accepted": 4,
       "cleanup": {
-        "deleted": 5,
+        "deleted": 4,
         "failed": []
       },
-      "fired at once": 8,
-      "reached running": 5,
-      "refused on the call": [
-        {
-          "elapsed_s": 0.78,
-          "index": 4,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-84268c9d-0fde-4834-8b56-c0fbb8b7ddd9\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.78,
-          "index": 7,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-d46f06a4-e435-4d84-aa7d-4c3a06013a36\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        },
-        {
-          "elapsed_s": 0.77,
-          "index": 8,
-          "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-81b94de9-3a4b-4a03-8ca0-5791e55dfa3f\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, reque",
-          "ok": false,
-          "raised": "UnprocessableError",
-          "status_code": 422
-        }
-      ],
+      "fired at once": 4,
+      "reached running": 4,
+      "refused on the call": [],
       "round": 3,
-      "task records left by the refused launches": {
-        "belonging to another run, left alone": [],
-        "ids": [
-          "0b1a541d-9774-43b9-9d66-e95b0214e5a6",
-          "89ffdecf-82ba-4381-b166-3ff9cde85471",
-          "fd84d4cf-cb74-4fa2-8c8b-6963ca5f2a71"
-        ],
-        "left behind": 3,
-        "removed": {
-          "deleted": 3,
-          "failed": []
-        }
-      },
-      "what the accepted ones settled to": {
-        "36df4b55-5a3f-40ec-b428-fd2bd4f19ad8": {
-          "reached": "running",
-          "seconds": 0.73
-        },
-        "7ad145e0-a8f9-4a99-bca6-53a8780af527": {
-          "reached": "running",
-          "seconds": 0.78
-        },
-        "8b221b5d-7842-48dd-a382-009fdcd4af45": {
-          "reached": "running",
-          "seconds": 0.71
-        },
-        "b55ecebf-5662-4c80-b204-17f7df63775b": {
-          "reached": "running",
-          "seconds": 0.73
-        },
-        "c8c9c143-d583-4d58-b90c-6d2447105820": {
-          "reached": "running",
-          "seconds": 0.71
-        }
-      }
-    },
-    {
-      "accepted": 3,
-      "cleanup": {
-        "deleted": 3,
-        "failed": []
-      },
-      "fired at once": 3,
-      "reached running": 3,
-      "refused on the call": [],
-      "round": 4,
       "task records left by the refused launches": {
         "belonging to another run, left alone": [],
         "ids": [],
@@ -12256,17 +12167,21 @@
         }
       },
       "what the accepted ones settled to": {
-        "38383ba4-79e0-42eb-bffe-1312e703ea91": {
+        "366a3577-5ace-4ae6-97a0-12cedcbc4645": {
           "reached": "running",
-          "seconds": 0.79
+          "seconds": 0.7
         },
-        "65de17d0-f516-423d-ae33-d6ecb8c41cb1": {
+        "b46bb133-0981-4176-ab54-3c4a93b86c02": {
           "reached": "running",
-          "seconds": 0.73
+          "seconds": 0.72
         },
-        "b9f685a7-ee32-44ec-ad57-7ec31a16a786": {
+        "ba4fcda3-a697-4695-be16-83157339a994": {
           "reached": "running",
-          "seconds": 0.79
+          "seconds": 0.72
+        },
+        "d51a55d2-42d5-4a01-9379-92cfc1ac90a2": {
+          "reached": "running",
+          "seconds": 0.76
         }
       }
     }
@@ -12299,26 +12214,26 @@
 {
   "hostnames claimed by more than one sandbox": "none",
   "id -&gt; hostname": {
-    "0e7f4e95-39da-49b1-a725-42773f89b7cd": "dbx_34U3okjGXhHZl3QqRixYq",
-    "36df4b55-5a3f-40ec-b428-fd2bd4f19ad8": "dbx_34U3pzc8jCZBBDr6ApDky",
-    "38383ba4-79e0-42eb-bffe-1312e703ea91": "dbx_34U3qOmtXTSSLgDgMTJ8Z",
-    "39b3b997-76d1-4587-8808-aa56b2fc332a": "dbx_34U3pTl5qRUU3xnTPgT6l",
-    "50595736-0f2a-4b57-8c21-e92fc1518644": "dbx_34U3pTlsBfcrUqC8hqpcC",
-    "65de17d0-f516-423d-ae33-d6ecb8c41cb1": "dbx_34U3qOm0uXwyJHKlw39UJ",
-    "7ad145e0-a8f9-4a99-bca6-53a8780af527": "dbx_34U3pzcKnXgrm6OlVPXbD",
-    "8b221b5d-7842-48dd-a382-009fdcd4af45": "dbx_34U3pzbSQxgbZWMd9VAtC",
-    "9433703f-f17b-4ce4-8a3a-c67d607aec20": "dbx_34U3okptBjNmJniZoOniC",
-    "98c28134-a6dd-4d74-9bfb-582e3f7ea582": "dbx_34U3okjSYae5756ibvKVZ",
-    "99d3e95f-7dce-4b8e-bfcb-64991dee4229": "dbx_34U3okhhm0eGqZc0Pj3kq",
-    "a8d041a7-459e-41c0-b6ad-e933e6f400d2": "dbx_34U3okg34vsuV0tHHJ5dP",
-    "b55ecebf-5662-4c80-b204-17f7df63775b": "dbx_34U3pzbkKM9tz2Pl44En4",
-    "b9f685a7-ee32-44ec-ad57-7ec31a16a786": "dbx_34U3qOj5e0jZxCqQHsJo8",
-    "c6bea9ee-65c1-406c-beb6-f2f3145b6fc7": "dbx_34U3pTkbYgnvNsr575eJ1",
-    "c8c9c143-d583-4d58-b90c-6d2447105820": "dbx_34U3pzdP7OJ6yWeQLS5oP",
-    "e34d7014-3a3f-4d29-9c20-c6abfbffad1a": "dbx_34U3okpbFtXYhx9ykvq9z",
-    "e536208f-3cb9-4bc5-ae7c-277743596648": "dbx_34U3pTmYOug12adVfb5cI",
-    "f8e9d7c7-3531-402a-9484-4911906cdc5f": "dbx_34U3pTls7lVNhAQ1mZTDv",
-    "fdcbc7fc-77a6-4cdf-9f1f-d7f547dd7522": "dbx_34U3okhnjdO0yRXkqB0QI"
+    "2d1b958e-9924-4afe-ba57-d088002353b2": "dbx_34U4OKQjs8LO8Z0zJvFst",
+    "366a3577-5ace-4ae6-97a0-12cedcbc4645": "dbx_34U4PgRmlYQj8oVw0bnwY",
+    "39f34309-4792-42be-845d-2fc13e4bed6e": "dbx_34U4P3hI0orwVt2u7tMfT",
+    "4bff9969-0d6d-4c5f-9d64-764ba998b414": "dbx_34U4P3h5uXZSipMlECXAr",
+    "59f7e41f-1e02-423a-9594-942bb0c00e12": "dbx_34U4OKU3YxegFcoTPxPq4",
+    "788a27c2-411b-4af3-b435-e7a1c298fd7a": "dbx_34U4P3ewvtoqBO70B3DA3",
+    "810cda4a-a33c-41b3-ace5-85eb8bacbc63": "dbx_34U4P3eqxQyDowHnVUQMB",
+    "8fe9a80f-d6e4-422b-b100-fb19bb37f710": "dbx_34U4OKY3HTw4GBWbkZuPy",
+    "903c5bae-5c9c-473a-957d-7b9c04bb85c9": "dbx_34U4OKQk7VEFKmYedkF8a",
+    "93a137d9-af1d-422e-85de-7bd894110911": "dbx_34U4P3g1WxT6BIG9sRzuf",
+    "96d26e2b-35d9-4796-bbe9-dbe5b8df54df": "dbx_34U4P3fdKt0KYKw3Xl6yu",
+    "a59441b6-a4bc-4a1b-94a7-49f92fbbf458": "dbx_34U4P3hsGjGGizMyq6wNX",
+    "a8f0e05d-a18c-4df1-ba77-7951653abfd0": "dbx_34U4OKXMsamDUkooa0lKA",
+    "b46bb133-0981-4176-ab54-3c4a93b86c02": "dbx_34U4PgRmvwC7dlU8bnvND",
+    "ba4fcda3-a697-4695-be16-83157339a994": "dbx_34U4PgRmfR7TPOuxb8siP",
+    "cabaebe7-8196-4581-9165-b29a38cb1f1e": "dbx_34U4OKTAy5lXjNHCPB58i",
+    "d15a7136-7d08-44ac-94d4-32cd2ea8facd": "dbx_34U4P3hOFXY7meXZaOo4p",
+    "d51a55d2-42d5-4a01-9379-92cfc1ac90a2": "dbx_34U4PgST27nVbKX9ARGXa",
+    "d93869b5-73a6-4620-b726-b7f0a57c7580": "dbx_34U4OKULbLkXQjMY0H4Jq",
+    "dac186d5-0952-44f8-95df-b7e2f87f01d0": "dbx_34U4P3j91hfUFYOCoz9tH"
   },
   "sandboxes that changed their answer": "none",
   "sandboxes that could not be asked at all": "none"
@@ -12348,9 +12263,9 @@
 {
   "admitted at once on the first round": 7,
   "checked": 20,
-  "largest number running at one time": 7,
-  "rounds used": 4,
-  "simultaneity this row could not reach": "the row asks for 20 at once and the quota admitted 7, so the identities below are distinct but were reached over 4 rounds",
+  "largest number running at one time": 9,
+  "rounds used": 3,
+  "simultaneity this row could not reach": "the row asks for 20 at once and the quota admitted 7, so the identities below are distinct but were reached over 3 rounds",
   "wanted": 20
 }</t>
         </is>
@@ -12384,7 +12299,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>PASSED - 4 of 4 steps. Run 2026-09-24 07:22 (UTC+8). 26.59s. billable - launched a real sandbox</t>
+          <t>PASSED - 4 of 4 steps. Run 2026-09-24 07:45 (UTC+8). 25.30s. billable - launched a real sandbox</t>
         </is>
       </c>
     </row>
@@ -12411,55 +12326,55 @@
     {
       "accepted": true,
       "attempt": 1,
-      "id": "bdf74ace-c5de-487b-b10e-c7bbdf2124eb",
+      "id": "25979a11-e907-49dd-8b22-4364325e8325",
       "settled": {
         "reached": "running",
-        "seconds": 0.77
+        "seconds": 0.78
       }
     },
     {
       "accepted": true,
       "attempt": 2,
-      "id": "81458769-3a3a-48dd-b3fc-bededb9b5962",
+      "id": "f4698e2e-e607-4cee-9c77-70d7a550516e",
       "settled": {
         "reached": "running",
-        "seconds": 0.76
+        "seconds": 0.78
       }
     },
     {
       "accepted": true,
       "attempt": 3,
-      "id": "bfbbf6de-4271-4e1e-8eec-8efe41fb5ec1",
+      "id": "45bbe4f8-9496-4c35-8f4c-4951effb9944",
       "settled": {
         "reached": "running",
-        "seconds": 0.76
+        "seconds": 0.78
       }
     },
     {
       "accepted": true,
       "attempt": 4,
-      "id": "9ef58c01-6da1-4bfc-86b9-c29a9ca3cc28",
-      "settled": {
-        "reached": "running",
-        "seconds": 0.74
-      }
-    },
-    {
-      "accepted": true,
-      "attempt": 5,
-      "id": "79f0cdc2-1722-4c73-9ee1-36b5933bb247",
+      "id": "d0af9801-c808-438e-a39a-4b67314796fb",
       "settled": {
         "reached": "running",
         "seconds": 0.72
       }
     },
     {
+      "accepted": true,
+      "attempt": 5,
+      "id": "990579e9-58ee-45ed-8aab-befa03b7b31a",
+      "settled": {
+        "reached": "running",
+        "seconds": 0.73
+      }
+    },
+    {
       "accepted": false,
       "attempt": 6,
       "code": null,
       "details": {},
-      "elapsed_s": 0.75,
-      "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-0489a952-3c2c-4076-9314-fdbd0b8b4f52\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, requested 1)\",\"trace_id\":\"a391149f7420938ad30de644fd54ec14\",\"details\":{\"idc_name\":\"sandbox-runloop-us\",\"q",
+      "elapsed_s": 0.76,
+      "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-105de7e5-d740-482c-8379-ffbec3a03082\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, requested 1)\",\"trace_id\":\"bf414f5e1c262368b3a6d938cfc6431a\",\"details\":{\"idc_name\":\"sandbox-runloop-us\",\"q",
       "raised": "UnprocessableError",
       "status_code": 422,
       "where": "on the launch call"
@@ -12469,8 +12384,8 @@
   "the refusal": {
     "code": null,
     "details": {},
-    "elapsed_s": 0.75,
-    "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-0489a952-3c2c-4076-9314-fdbd0b8b4f52\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, requested 1)\",\"trace_id\":\"a391149f7420938ad30de644fd54ec14\",\"details\":{\"idc_name\":\"sandbox-runloop-us\",\"q",
+    "elapsed_s": 0.76,
+    "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-105de7e5-d740-482c-8379-ffbec3a03082\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, requested 1)\",\"trace_id\":\"bf414f5e1c262368b3a6d938cfc6431a\",\"details\":{\"idc_name\":\"sandbox-runloop-us\",\"q",
     "raised": "UnprocessableError",
     "status_code": 422,
     "where": "on the launch call"
@@ -12502,12 +12417,12 @@
           <t>PASSED
 {
   "names quota": true,
-  "reason": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-0489a952-3c2c-4076-9314-fdbd0b8b4f52\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, requested 1)\",\"trace_id\":\"a391149f7420938ad30de644fd54ec14\",\"details\":{\"idc_name\":\"sandbox-runloop-us\",\"q",
+  "reason": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-105de7e5-d740-482c-8379-ffbec3a03082\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, requested 1)\",\"trace_id\":\"bf414f5e1c262368b3a6d938cfc6431a\",\"details\":{\"idc_name\":\"sandbox-runloop-us\",\"q",
   "refusal": {
     "code": null,
     "details": {},
-    "elapsed_s": 0.75,
-    "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-0489a952-3c2c-4076-9314-fdbd0b8b4f52\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, requested 1)\",\"trace_id\":\"a391149f7420938ad30de644fd54ec14\",\"details\":{\"idc_name\":\"sandbox-runloop-us\",\"q",
+    "elapsed_s": 0.76,
+    "message": "upstream create container: business-cloud-api https://ce-tot.gmicloud-dev.com/api/v2/sandboxes returned 429: {\"request_id\":\"req-105de7e5-d740-482c-8379-ffbec3a03082\",\"code\":\"Resource.QuotaExceeded\",\"message\":\"sandbox quota exceeded: instance_type gmi.sandbox.x-small in sandbox-runloop-us (5/5, requested 1)\",\"trace_id\":\"bf414f5e1c262368b3a6d938cfc6431a\",\"details\":{\"idc_name\":\"sandbox-runloop-us\",\"q",
     "raised": "UnprocessableError",
     "status_code": 422,
     "where": "on the launch call"
@@ -12515,22 +12430,22 @@
 }
 {
   "records found by difference": [
-    "584488dd-479e-416a-a3b8-6c150d8faed9",
-    "79f0cdc2-1722-4c73-9ee1-36b5933bb247",
-    "81458769-3a3a-48dd-b3fc-bededb9b5962",
-    "9ef58c01-6da1-4bfc-86b9-c29a9ca3cc28",
-    "bdf74ace-c5de-487b-b10e-c7bbdf2124eb",
-    "bfbbf6de-4271-4e1e-8eec-8efe41fb5ec1"
+    "14406b28-ea60-4795-9a61-950c5ba1a16a",
+    "25979a11-e907-49dd-8b22-4364325e8325",
+    "45bbe4f8-9496-4c35-8f4c-4951effb9944",
+    "990579e9-58ee-45ed-8aab-befa03b7b31a",
+    "d0af9801-c808-438e-a39a-4b67314796fb",
+    "f4698e2e-e607-4cee-9c77-70d7a550516e"
   ],
   "records no caller ever saw an id for": [
-    "584488dd-479e-416a-a3b8-6c150d8faed9"
+    "14406b28-ea60-4795-9a61-950c5ba1a16a"
   ],
   "sandboxes this row is holding an id for": [
-    "bdf74ace-c5de-487b-b10e-c7bbdf2124eb",
-    "81458769-3a3a-48dd-b3fc-bededb9b5962",
-    "bfbbf6de-4271-4e1e-8eec-8efe41fb5ec1",
-    "9ef58c01-6da1-4bfc-86b9-c29a9ca3cc28",
-    "79f0cdc2-1722-4c73-9ee1-36b5933bb247"
+    "25979a11-e907-49dd-8b22-4364325e8325",
+    "f4698e2e-e607-4cee-9c77-70d7a550516e",
+    "45bbe4f8-9496-4c35-8f4c-4951effb9944",
+    "d0af9801-c808-438e-a39a-4b67314796fb",
+    "990579e9-58ee-45ed-8aab-befa03b7b31a"
   ],
   "why this matters": "a launch refused on the call still creates a task record, and the SDK raised rather than returning its id — so the only way to find one is to list the whole account and subtract what you know about"
 }</t>
@@ -12563,11 +12478,11 @@
   "failed": []
 }
 {
-  "id": "5b664b00-ef69-4561-89db-46a9158ed934",
-  "seconds from delete to running": 2.37,
+  "id": "2ced273f-bd53-4f74-998f-16c585279c9b",
+  "seconds from delete to running": 2.17,
   "settled": {
     "reached": "running",
-    "seconds": 0.82
+    "seconds": 0.72
   }
 }</t>
         </is>
